--- a/KatalonData/ABPTestData/SchedulePaymentABP_NoCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_NoCF.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="75">
   <si>
     <t>Result</t>
   </si>
@@ -335,6 +335,24 @@
   </si>
   <si>
     <t>Fri Sep 18 01:37:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:44:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:47:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:49:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:50:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:03:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:05:09 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -778,7 +796,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -926,7 +944,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1068,7 +1086,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1211,7 +1229,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">

--- a/KatalonData/ABPTestData/SchedulePaymentABP_NoCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_NoCF.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{4C57AE5B-CA0B-43A5-8CB0-ABB6D4F0843E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C57AE5B-CA0B-43A5-8CB0-ABB6D4F0843E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CVCSPNoCFPS_RecMonthly" r:id="rId1" sheetId="1"/>
-    <sheet name="CVCSPNoCFCC_RecMonthly" r:id="rId2" sheetId="2"/>
-    <sheet name="CVCSPNoCFPC_RecMonthly" r:id="rId3" sheetId="3"/>
-    <sheet name="CVCSPNoCFCorp_RecMonthly" r:id="rId4" sheetId="4"/>
+    <sheet name="CVCSPNoCFPS_RecMonthly" sheetId="1" r:id="rId1"/>
+    <sheet name="CVCSPNoCFCC_RecMonthly" sheetId="2" r:id="rId2"/>
+    <sheet name="CVCSPNoCFPC_RecMonthly" sheetId="3" r:id="rId3"/>
+    <sheet name="CVCSPNoCFCorp_RecMonthly" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="29">
   <si>
     <t>Result</t>
   </si>
@@ -180,18 +180,6 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
-    <t>Sun Oct 26 19:53:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 20:39:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 20:44:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 13 22:10:42 IST 2025</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 180RemittanceID: 916-151942,
 1. Review bill to pay,
@@ -217,133 +205,7 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thu Nov 13 22:25:03 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 17 15:00:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:58:19 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:59:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:00:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:02:01 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 03:08:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 03:13:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 03:19:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 03:26:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:45:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:46:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:48:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:49:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 02:30:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 02:31:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 02:33:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 02:34:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 12:48:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 12:49:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 12:50:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 12:52:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 24 22:46:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 24 22:48:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 24 22:51:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 24 22:54:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 20:07:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 20:08:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 20:09:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 20:10:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 01:16:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 01:17:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 01:18:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 01:19:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 01:33:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 01:34:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 01:35:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 01:37:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 25 15:44:55 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Sep 25 15:47:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 25 15:49:01 IST 2026</t>
   </si>
   <si>
     <t>Fri Sep 25 15:50:55 IST 2026</t>
@@ -421,46 +283,46 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="164" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="2" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -477,10 +339,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -515,7 +377,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -550,7 +412,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -644,21 +506,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -675,7 +537,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -727,21 +589,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="23.54296875" collapsed="true"/>
+    <col min="11" max="11" width="23.54296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,13 +625,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -791,12 +653,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>72</v>
+      <c r="B2" t="s">
+        <v>26</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -808,25 +670,25 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>11/14/2025</v>
+        <v>10/13/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -858,7 +720,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 11/14/2025,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 11/14/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 10/13/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -866,13 +728,13 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 11/14/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -880,16 +742,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CD28ED-6B88-4076-A023-4B2AA175CC49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CD28ED-6B88-4076-A023-4B2AA175CC49}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="5.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" width="26.453125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" width="23.7265625" collapsed="true"/>
+    <col min="3" max="3" width="5.6328125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="26.453125" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="23.7265625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,13 +773,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -939,12 +801,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>73</v>
+      <c r="B2" t="s">
+        <v>27</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -956,17 +818,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -974,7 +836,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>11/14/2025</v>
+        <v>10/13/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1005,7 +867,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 11/14/2025,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 11/14/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 10/13/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1013,25 +875,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 11/14/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38E6C38-F14D-4B06-9F0D-017FEF3E0BF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38E6C38-F14D-4B06-9F0D-017FEF3E0BF1}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="32.90625" collapsed="true"/>
+    <col min="11" max="11" width="32.90625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,13 +915,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1081,12 +943,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>74</v>
+      <c r="B2" t="s">
+        <v>28</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1098,17 +960,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1116,7 +978,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>11/14/2025</v>
+        <v>10/13/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1148,7 +1010,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 11/14/2025,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 11/14/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 10/13/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1156,25 +1018,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 11/14/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACB12DE-9459-4B21-A76D-74D1C2CFA77A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACB12DE-9459-4B21-A76D-74D1C2CFA77A}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="20.81640625" collapsed="true"/>
+    <col min="11" max="11" width="20.81640625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1196,13 +1058,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1224,12 +1086,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>70</v>
+      <c r="B2" t="s">
+        <v>25</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1241,17 +1103,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str" s="0">
+      <c r="G2" t="str">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1259,7 +1121,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>11/14/2025</v>
+        <v>10/13/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1293,7 +1155,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 11/14/2025,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 11/14/2025 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 10/13/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1301,12 +1163,12 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 11/14/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 0.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>